--- a/xls/Pontius.xlsx
+++ b/xls/Pontius.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\OneDrive\Documentos\estatistica2024\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2025/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_00243C141A561EB39BEA2655A4FC3EF71297758D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DC26D3F-4019-4DA1-9AE7-E39AF7C18F4A}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="600" windowWidth="12210" windowHeight="7965"/>
+    <workbookView xWindow="675" yWindow="2085" windowWidth="26610" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="matriz_conf" sheetId="4" r:id="rId1"/>
@@ -26,12 +27,25 @@
     <definedName name="nit">#REF!</definedName>
     <definedName name="nti">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="26">
   <si>
     <t>A</t>
   </si>
@@ -101,11 +115,20 @@
   <si>
     <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2024</t>
   </si>
+  <si>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2025</t>
+  </si>
+  <si>
+    <t>#http://urlib.net/8JMKD2USNRW34T/4D6DMD2</t>
+  </si>
+  <si>
+    <t>#https://cdrenno.github.io/Estatistica/</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
@@ -118,6 +141,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -611,15 +635,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -628,7 +651,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -780,7 +803,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -820,7 +843,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
@@ -901,6 +924,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5C0D-4A40-9281-E23F050AC24D}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -963,6 +991,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5C0D-4A40-9281-E23F050AC24D}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -1025,6 +1058,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5C0D-4A40-9281-E23F050AC24D}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1082,7 +1120,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:txPr>
         <a:bodyPr/>
@@ -1129,7 +1166,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4106" name="Gráfico 1"/>
+        <xdr:cNvPr id="4106" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A100000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -1150,9 +1193,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Escritório">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1190,9 +1233,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Escritório">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1227,7 +1270,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1262,7 +1305,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Escritório">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1435,476 +1478,446 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:P25"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="2.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="2" customWidth="1"/>
-    <col min="4" max="7" width="8.140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="3" style="2" customWidth="1"/>
-    <col min="9" max="10" width="8.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="2.42578125" style="2" customWidth="1"/>
-    <col min="12" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="2" width="2.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="1" customWidth="1"/>
+    <col min="4" max="7" width="8.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="3" style="1" customWidth="1"/>
+    <col min="9" max="10" width="8.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="2.42578125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="6"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="70" t="s">
+    <row r="1" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5"/>
+      <c r="D3" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="71" t="s">
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="1"/>
-      <c r="N4" s="74" t="s">
+      <c r="I4" s="9"/>
+      <c r="J4" s="10"/>
+      <c r="N4" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="O4" s="75"/>
-      <c r="P4" s="76"/>
-    </row>
-    <row r="5" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="71"/>
-      <c r="C5" s="7" t="str">
+      <c r="O4" s="74"/>
+      <c r="P4" s="75"/>
+    </row>
+    <row r="5" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="70"/>
+      <c r="C5" s="6" t="str">
         <f>D4</f>
         <v>A</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <v>13</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="17">
         <v>8</v>
       </c>
-      <c r="F5" s="18">
-        <v>0</v>
-      </c>
-      <c r="G5" s="24">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="19">
+      <c r="F5" s="17">
+        <v>0</v>
+      </c>
+      <c r="G5" s="23">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="18">
         <f>SUM(D5:G5)</f>
         <v>21</v>
       </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="1"/>
-      <c r="M5" s="59" t="str">
+      <c r="J5" s="10"/>
+      <c r="M5" s="58" t="str">
         <f>C5</f>
         <v>A</v>
       </c>
-      <c r="N5" s="62">
+      <c r="N5" s="61">
         <v>0.25</v>
       </c>
-      <c r="O5" s="54">
+      <c r="O5" s="53">
         <v>0.01</v>
       </c>
-      <c r="P5" s="55">
+      <c r="P5" s="54">
         <v>0.01</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="71"/>
-      <c r="C6" s="7" t="str">
+    <row r="6" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="70"/>
+      <c r="C6" s="6" t="str">
         <f>E4</f>
         <v>B</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <v>8</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <v>10</v>
       </c>
-      <c r="F6" s="21">
-        <v>0</v>
-      </c>
-      <c r="G6" s="25">
+      <c r="F6" s="20">
+        <v>0</v>
+      </c>
+      <c r="G6" s="24">
         <v>3</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="19">
+      <c r="H6" s="6"/>
+      <c r="I6" s="18">
         <f>SUM(D6:G6)</f>
         <v>21</v>
       </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="1"/>
-      <c r="M6" s="60" t="str">
+      <c r="J6" s="10"/>
+      <c r="M6" s="59" t="str">
         <f>C6</f>
         <v>B</v>
       </c>
-      <c r="N6" s="63">
+      <c r="N6" s="62">
         <v>0.25</v>
       </c>
-      <c r="O6" s="53">
+      <c r="O6" s="52">
         <v>0.02</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="55">
         <v>0.95</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="71"/>
-      <c r="C7" s="7" t="str">
+    <row r="7" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="70"/>
+      <c r="C7" s="6" t="str">
         <f>F4</f>
         <v>C</v>
       </c>
-      <c r="D7" s="20">
-        <v>0</v>
-      </c>
-      <c r="E7" s="21">
+      <c r="D7" s="19">
+        <v>0</v>
+      </c>
+      <c r="E7" s="20">
         <v>5</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="20">
         <v>27</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="24">
         <v>4</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="19">
+      <c r="H7" s="6"/>
+      <c r="I7" s="18">
         <f>SUM(D7:G7)</f>
         <v>36</v>
       </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="1"/>
-      <c r="M7" s="60" t="str">
+      <c r="J7" s="10"/>
+      <c r="M7" s="59" t="str">
         <f>C7</f>
         <v>C</v>
       </c>
-      <c r="N7" s="63">
+      <c r="N7" s="62">
         <v>0.25</v>
       </c>
-      <c r="O7" s="53">
+      <c r="O7" s="52">
         <v>0.95</v>
       </c>
-      <c r="P7" s="56">
+      <c r="P7" s="55">
         <v>0.03</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="71"/>
-      <c r="C8" s="7" t="str">
+    <row r="8" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="70"/>
+      <c r="C8" s="6" t="str">
         <f>G4</f>
         <v>D</v>
       </c>
-      <c r="D8" s="26">
-        <v>0</v>
-      </c>
-      <c r="E8" s="27">
-        <v>0</v>
-      </c>
-      <c r="F8" s="27">
-        <v>0</v>
-      </c>
-      <c r="G8" s="28">
+      <c r="D8" s="25">
+        <v>0</v>
+      </c>
+      <c r="E8" s="26">
+        <v>0</v>
+      </c>
+      <c r="F8" s="26">
+        <v>0</v>
+      </c>
+      <c r="G8" s="27">
         <v>32</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="19">
+      <c r="H8" s="6"/>
+      <c r="I8" s="18">
         <f>SUM(D8:G8)</f>
         <v>32</v>
       </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="1"/>
-      <c r="M8" s="61" t="str">
+      <c r="J8" s="10"/>
+      <c r="M8" s="60" t="str">
         <f>C8</f>
         <v>D</v>
       </c>
-      <c r="N8" s="64">
+      <c r="N8" s="63">
         <f>1-SUM(N5:N7)</f>
         <v>0.25</v>
       </c>
-      <c r="O8" s="57">
+      <c r="O8" s="56">
         <f>1-SUM(O5:O7)</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="P8" s="58">
+      <c r="P8" s="57">
         <f>1-SUM(P5:P7)</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="71"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="1"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-    </row>
-    <row r="10" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="9"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="19">
+    <row r="9" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="70"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="10"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+    </row>
+    <row r="10" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="18">
         <f>SUM(D5:D8)</f>
         <v>21</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="18">
         <f>SUM(E5:E8)</f>
         <v>23</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="18">
         <f>SUM(F5:F8)</f>
         <v>27</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="18">
         <f>SUM(G5:G8)</f>
         <v>39</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="22">
+      <c r="H10" s="6"/>
+      <c r="I10" s="21">
         <f>SUM(D5:G8)</f>
         <v>110</v>
       </c>
-      <c r="J10" s="11"/>
-      <c r="K10" s="1"/>
-      <c r="M10" s="12" t="s">
+      <c r="J10" s="10"/>
+      <c r="M10" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="N10" s="66">
+      <c r="N10" s="65">
         <f>$D17*N5+$D18*N6+$D19*N7+$D20*N8</f>
         <v>0.7185857620640228</v>
       </c>
-      <c r="O10" s="66">
+      <c r="O10" s="65">
         <f>$D17*O5+$D18*O6+$D19*O7+$D20*O8</f>
         <v>0.98129638477464554</v>
       </c>
-      <c r="P10" s="67">
+      <c r="P10" s="66">
         <f>$D17*P5+$D18*P6+$D19*P7+$D20*P8</f>
         <v>0.45743908265647393</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="9"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="6"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="52" t="s">
+    <row r="11" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="5"/>
+      <c r="D12" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="22">
         <f>(D5+E6+F7+G8)/I10</f>
         <v>0.74545454545454548</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="13"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="72" t="s">
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="12"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="35" t="s">
+      <c r="G15" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="16"/>
-    </row>
-    <row r="16" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="36" t="s">
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C16" s="72"/>
+      <c r="D16" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="36" t="s">
+      <c r="F16" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="43" t="s">
+      <c r="G16" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="16"/>
-    </row>
-    <row r="17" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="37" t="str">
+      <c r="H16" s="15"/>
+    </row>
+    <row r="17" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="36" t="str">
         <f>D4</f>
         <v>A</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="39">
         <f>D5/D10</f>
         <v>0.61904761904761907</v>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="39">
         <f>1-D17</f>
         <v>0.38095238095238093</v>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="39">
         <f>D5/I5</f>
         <v>0.61904761904761907</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="43">
         <f>1-F17</f>
         <v>0.38095238095238093</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="38" t="str">
+    <row r="18" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="37" t="str">
         <f>E4</f>
         <v>B</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="40">
         <f>E6/E10</f>
         <v>0.43478260869565216</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="40">
         <f>1-D18</f>
         <v>0.56521739130434789</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="40">
         <f>E6/I6</f>
         <v>0.47619047619047616</v>
       </c>
-      <c r="G18" s="45">
+      <c r="G18" s="44">
         <f>1-F18</f>
         <v>0.52380952380952384</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="38" t="str">
+    <row r="19" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="37" t="str">
         <f>F4</f>
         <v>C</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="40">
         <f>F7/F10</f>
         <v>1</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="40">
         <f>1-D19</f>
         <v>0</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="40">
         <f>F7/I7</f>
         <v>0.75</v>
       </c>
-      <c r="G19" s="45">
+      <c r="G19" s="44">
         <f>1-F19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C20" s="39" t="str">
+    <row r="20" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C20" s="38" t="str">
         <f>G4</f>
         <v>D</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="41">
         <f>G8/G10</f>
         <v>0.82051282051282048</v>
       </c>
-      <c r="E20" s="42">
+      <c r="E20" s="41">
         <f>1-D20</f>
         <v>0.17948717948717952</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="41">
         <f>G8/I8</f>
         <v>1</v>
       </c>
-      <c r="G20" s="46">
+      <c r="G20" s="45">
         <f>1-F20</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C23" s="69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C24" s="69" t="s">
-        <v>21</v>
+    <row r="23" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C25" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1920,841 +1933,757 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B1:AE21"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="2.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="2" customWidth="1"/>
-    <col min="4" max="7" width="8.140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="3" style="2" customWidth="1"/>
-    <col min="9" max="10" width="8.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="2.42578125" style="2" customWidth="1"/>
+    <col min="1" max="2" width="2.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="1" customWidth="1"/>
+    <col min="4" max="7" width="8.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="3" style="1" customWidth="1"/>
+    <col min="9" max="10" width="8.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="2.42578125" style="1" customWidth="1"/>
     <col min="12" max="12" width="9.140625" style="1"/>
-    <col min="13" max="13" width="2.28515625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.42578125" style="2" customWidth="1"/>
-    <col min="15" max="18" width="8.140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="3" style="2" customWidth="1"/>
-    <col min="20" max="21" width="8.140625" style="2" customWidth="1"/>
-    <col min="22" max="22" width="2.42578125" style="2" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" style="2"/>
-    <col min="24" max="24" width="2.28515625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="7.42578125" style="2" customWidth="1"/>
-    <col min="26" max="29" width="8.140625" style="2" customWidth="1"/>
-    <col min="30" max="30" width="3" style="2" customWidth="1"/>
-    <col min="31" max="31" width="2.42578125" style="2" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="2"/>
+    <col min="13" max="13" width="2.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.42578125" style="1" customWidth="1"/>
+    <col min="15" max="18" width="8.140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="3" style="1" customWidth="1"/>
+    <col min="20" max="21" width="8.140625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="2.42578125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.140625" style="1"/>
+    <col min="24" max="24" width="2.28515625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="7.42578125" style="1" customWidth="1"/>
+    <col min="26" max="29" width="8.140625" style="1" customWidth="1"/>
+    <col min="30" max="30" width="3" style="1" customWidth="1"/>
+    <col min="31" max="31" width="2.42578125" style="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="1"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4" t="s">
+    <row r="1" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="4"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="1"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4" t="s">
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="4"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="5"/>
-    </row>
-    <row r="3" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="6"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="70" t="s">
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="4"/>
+    </row>
+    <row r="3" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="5"/>
+      <c r="D3" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="7"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="70" t="s">
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="6"/>
+      <c r="M3" s="5"/>
+      <c r="O3" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="70"/>
-      <c r="Q3" s="70"/>
-      <c r="R3" s="70"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="7"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="70" t="s">
+      <c r="P3" s="69"/>
+      <c r="Q3" s="69"/>
+      <c r="R3" s="69"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="6"/>
+      <c r="X3" s="5"/>
+      <c r="Z3" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="AA3" s="70"/>
-      <c r="AB3" s="70"/>
-      <c r="AC3" s="70"/>
-      <c r="AD3" s="7"/>
-      <c r="AE3" s="8"/>
-    </row>
-    <row r="4" spans="1:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="71" t="s">
+      <c r="AA3" s="69"/>
+      <c r="AB3" s="69"/>
+      <c r="AC3" s="69"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="7"/>
+    </row>
+    <row r="4" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="1"/>
-      <c r="M4" s="71" t="s">
+      <c r="I4" s="9"/>
+      <c r="J4" s="10"/>
+      <c r="M4" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="1"/>
-      <c r="O4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="P4" s="7" t="s">
+      <c r="O4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="P4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="Q4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="R4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="S4" s="1"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="1"/>
-      <c r="X4" s="71" t="s">
+      <c r="T4" s="9"/>
+      <c r="U4" s="10"/>
+      <c r="X4" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="7" t="s">
+      <c r="Z4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="AB4" s="7" t="s">
+      <c r="AB4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AC4" s="7" t="s">
+      <c r="AC4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="11"/>
-    </row>
-    <row r="5" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="71"/>
-      <c r="C5" s="7" t="str">
+      <c r="AE4" s="10"/>
+    </row>
+    <row r="5" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="70"/>
+      <c r="C5" s="6" t="str">
         <f>D4</f>
         <v>A</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <f>matriz_conf!D5</f>
         <v>13</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="17">
         <f>matriz_conf!E5</f>
         <v>8</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="17">
         <f>matriz_conf!F5</f>
         <v>0</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="23">
         <f>matriz_conf!G5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="19">
+      <c r="H5" s="6"/>
+      <c r="I5" s="18">
         <f>SUM(D5:G5)</f>
         <v>21</v>
       </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="1"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="7" t="str">
+      <c r="J5" s="10"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="6" t="str">
         <f>O4</f>
         <v>A</v>
       </c>
-      <c r="O5" s="29">
+      <c r="O5" s="28">
         <f t="shared" ref="O5:R8" si="0">D5/$I$10</f>
         <v>0.11818181818181818</v>
       </c>
-      <c r="P5" s="30">
+      <c r="P5" s="29">
         <f t="shared" si="0"/>
         <v>7.2727272727272724E-2</v>
       </c>
-      <c r="Q5" s="18">
+      <c r="Q5" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R5" s="24">
+      <c r="R5" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S5" s="7"/>
-      <c r="T5" s="48">
+      <c r="S5" s="6"/>
+      <c r="T5" s="47">
         <f>SUM(O5:R5)</f>
         <v>0.19090909090909092</v>
       </c>
-      <c r="U5" s="11"/>
-      <c r="V5" s="1"/>
-      <c r="X5" s="71"/>
-      <c r="Y5" s="7" t="str">
+      <c r="U5" s="10"/>
+      <c r="X5" s="70"/>
+      <c r="Y5" s="6" t="str">
         <f>Z4</f>
         <v>A</v>
       </c>
-      <c r="Z5" s="17">
+      <c r="Z5" s="16">
         <f>MIN(D5,D5)</f>
         <v>13</v>
       </c>
-      <c r="AA5" s="18">
+      <c r="AA5" s="17">
         <f>MIN(E5,D6)</f>
         <v>8</v>
       </c>
-      <c r="AB5" s="18">
+      <c r="AB5" s="17">
         <f>MIN(F5,D7)</f>
         <v>0</v>
       </c>
-      <c r="AC5" s="24">
+      <c r="AC5" s="23">
         <f>MIN(G5,D8)</f>
         <v>0</v>
       </c>
-      <c r="AD5" s="7"/>
-      <c r="AE5" s="11"/>
-    </row>
-    <row r="6" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="71"/>
-      <c r="C6" s="7" t="str">
+      <c r="AD5" s="6"/>
+      <c r="AE5" s="10"/>
+    </row>
+    <row r="6" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="70"/>
+      <c r="C6" s="6" t="str">
         <f>E4</f>
         <v>B</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <f>matriz_conf!D6</f>
         <v>8</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <f>matriz_conf!E6</f>
         <v>10</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="20">
         <f>matriz_conf!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="24">
         <f>matriz_conf!G6</f>
         <v>3</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="19">
+      <c r="H6" s="6"/>
+      <c r="I6" s="18">
         <f>SUM(D6:G6)</f>
         <v>21</v>
       </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="1"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="7" t="str">
+      <c r="J6" s="10"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="6" t="str">
         <f>P4</f>
         <v>B</v>
       </c>
-      <c r="O6" s="31">
+      <c r="O6" s="30">
         <f t="shared" si="0"/>
         <v>7.2727272727272724E-2</v>
       </c>
-      <c r="P6" s="32">
+      <c r="P6" s="31">
         <f t="shared" si="0"/>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="Q6" s="21">
+      <c r="Q6" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R6" s="25">
+      <c r="R6" s="24">
         <f t="shared" si="0"/>
         <v>2.7272727272727271E-2</v>
       </c>
-      <c r="S6" s="7"/>
-      <c r="T6" s="48">
+      <c r="S6" s="6"/>
+      <c r="T6" s="47">
         <f>SUM(O6:R6)</f>
         <v>0.19090909090909092</v>
       </c>
-      <c r="U6" s="11"/>
-      <c r="V6" s="1"/>
-      <c r="X6" s="71"/>
-      <c r="Y6" s="7" t="str">
+      <c r="U6" s="10"/>
+      <c r="X6" s="70"/>
+      <c r="Y6" s="6" t="str">
         <f>AA4</f>
         <v>B</v>
       </c>
-      <c r="Z6" s="20">
+      <c r="Z6" s="19">
         <f>MIN(D6,E5)</f>
         <v>8</v>
       </c>
-      <c r="AA6" s="21">
+      <c r="AA6" s="20">
         <f>MIN(E6,E6)</f>
         <v>10</v>
       </c>
-      <c r="AB6" s="21">
+      <c r="AB6" s="20">
         <f>MIN(F6,E7)</f>
         <v>0</v>
       </c>
-      <c r="AC6" s="25">
+      <c r="AC6" s="24">
         <f>MIN(G6,E8)</f>
         <v>0</v>
       </c>
-      <c r="AD6" s="7"/>
-      <c r="AE6" s="11"/>
-    </row>
-    <row r="7" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="71"/>
-      <c r="C7" s="7" t="str">
+      <c r="AD6" s="6"/>
+      <c r="AE6" s="10"/>
+    </row>
+    <row r="7" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="70"/>
+      <c r="C7" s="6" t="str">
         <f>F4</f>
         <v>C</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <f>matriz_conf!D7</f>
         <v>0</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="20">
         <f>matriz_conf!E7</f>
         <v>5</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="20">
         <f>matriz_conf!F7</f>
         <v>27</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="24">
         <f>matriz_conf!G7</f>
         <v>4</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="19">
+      <c r="H7" s="6"/>
+      <c r="I7" s="18">
         <f>SUM(D7:G7)</f>
         <v>36</v>
       </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="1"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="7" t="str">
+      <c r="J7" s="10"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="6" t="str">
         <f>Q4</f>
         <v>C</v>
       </c>
-      <c r="O7" s="20">
+      <c r="O7" s="19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P7" s="32">
+      <c r="P7" s="31">
         <f t="shared" si="0"/>
         <v>4.5454545454545456E-2</v>
       </c>
-      <c r="Q7" s="32">
+      <c r="Q7" s="31">
         <f t="shared" si="0"/>
         <v>0.24545454545454545</v>
       </c>
-      <c r="R7" s="33">
+      <c r="R7" s="32">
         <f t="shared" si="0"/>
         <v>3.6363636363636362E-2</v>
       </c>
-      <c r="S7" s="7"/>
-      <c r="T7" s="48">
+      <c r="S7" s="6"/>
+      <c r="T7" s="47">
         <f>SUM(O7:R7)</f>
         <v>0.32727272727272727</v>
       </c>
-      <c r="U7" s="11"/>
-      <c r="V7" s="1"/>
-      <c r="X7" s="71"/>
-      <c r="Y7" s="7" t="str">
+      <c r="U7" s="10"/>
+      <c r="X7" s="70"/>
+      <c r="Y7" s="6" t="str">
         <f>AB4</f>
         <v>C</v>
       </c>
-      <c r="Z7" s="20">
+      <c r="Z7" s="19">
         <f>MIN(D7,F5)</f>
         <v>0</v>
       </c>
-      <c r="AA7" s="21">
+      <c r="AA7" s="20">
         <f>MIN(E7,F6)</f>
         <v>0</v>
       </c>
-      <c r="AB7" s="21">
+      <c r="AB7" s="20">
         <f>MIN(F7,F7)</f>
         <v>27</v>
       </c>
-      <c r="AC7" s="25">
+      <c r="AC7" s="24">
         <f>MIN(G7,F8)</f>
         <v>0</v>
       </c>
-      <c r="AD7" s="7"/>
-      <c r="AE7" s="11"/>
-    </row>
-    <row r="8" spans="1:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="71"/>
-      <c r="C8" s="7" t="str">
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="10"/>
+    </row>
+    <row r="8" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="70"/>
+      <c r="C8" s="6" t="str">
         <f>G4</f>
         <v>D</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <f>matriz_conf!D8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="26">
         <f>matriz_conf!E8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="26">
         <f>matriz_conf!F8</f>
         <v>0</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="27">
         <f>matriz_conf!G8</f>
         <v>32</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="19">
+      <c r="H8" s="6"/>
+      <c r="I8" s="18">
         <f>SUM(D8:G8)</f>
         <v>32</v>
       </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="1"/>
-      <c r="M8" s="71"/>
-      <c r="N8" s="7" t="str">
+      <c r="J8" s="10"/>
+      <c r="M8" s="70"/>
+      <c r="N8" s="6" t="str">
         <f>R4</f>
         <v>D</v>
       </c>
-      <c r="O8" s="26">
+      <c r="O8" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P8" s="27">
+      <c r="P8" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q8" s="27">
+      <c r="Q8" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R8" s="34">
+      <c r="R8" s="33">
         <f t="shared" si="0"/>
         <v>0.29090909090909089</v>
       </c>
-      <c r="S8" s="7"/>
-      <c r="T8" s="48">
+      <c r="S8" s="6"/>
+      <c r="T8" s="47">
         <f>SUM(O8:R8)</f>
         <v>0.29090909090909089</v>
       </c>
-      <c r="U8" s="11"/>
-      <c r="V8" s="1"/>
-      <c r="X8" s="71"/>
-      <c r="Y8" s="7" t="str">
+      <c r="U8" s="10"/>
+      <c r="X8" s="70"/>
+      <c r="Y8" s="6" t="str">
         <f>AC4</f>
         <v>D</v>
       </c>
-      <c r="Z8" s="26">
+      <c r="Z8" s="25">
         <f>MIN(D8,G5)</f>
         <v>0</v>
       </c>
-      <c r="AA8" s="27">
+      <c r="AA8" s="26">
         <f>MIN(E8,G6)</f>
         <v>0</v>
       </c>
-      <c r="AB8" s="27">
+      <c r="AB8" s="26">
         <f>MIN(F8,G7)</f>
         <v>0</v>
       </c>
-      <c r="AC8" s="28">
+      <c r="AC8" s="27">
         <f>MIN(G8,G8)</f>
         <v>32</v>
       </c>
-      <c r="AD8" s="7"/>
-      <c r="AE8" s="11"/>
-    </row>
-    <row r="9" spans="1:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="71"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="1"/>
-      <c r="M9" s="71"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="1"/>
-      <c r="X9" s="71"/>
-      <c r="Y9" s="1"/>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
-      <c r="AC9" s="7"/>
-      <c r="AD9" s="7"/>
-      <c r="AE9" s="11"/>
-    </row>
-    <row r="10" spans="1:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="9"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="19">
+      <c r="AD8" s="6"/>
+      <c r="AE8" s="10"/>
+    </row>
+    <row r="9" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="70"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="10"/>
+      <c r="M9" s="70"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="10"/>
+      <c r="X9" s="70"/>
+      <c r="Z9" s="6"/>
+      <c r="AA9" s="6"/>
+      <c r="AB9" s="6"/>
+      <c r="AC9" s="6"/>
+      <c r="AD9" s="6"/>
+      <c r="AE9" s="10"/>
+    </row>
+    <row r="10" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="18">
         <f>SUM(D5:D8)</f>
         <v>21</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="18">
         <f>SUM(E5:E8)</f>
         <v>23</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="18">
         <f>SUM(F5:F8)</f>
         <v>27</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="18">
         <f>SUM(G5:G8)</f>
         <v>39</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="22">
+      <c r="H10" s="6"/>
+      <c r="I10" s="21">
         <f>SUM(D5:G8)</f>
         <v>110</v>
       </c>
-      <c r="J10" s="11"/>
-      <c r="K10" s="1"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="48">
+      <c r="J10" s="10"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="47">
         <f>SUM(O5:O8)</f>
         <v>0.19090909090909092</v>
       </c>
-      <c r="P10" s="48">
+      <c r="P10" s="47">
         <f>SUM(P5:P8)</f>
         <v>0.20909090909090911</v>
       </c>
-      <c r="Q10" s="48">
+      <c r="Q10" s="47">
         <f>SUM(Q5:Q8)</f>
         <v>0.24545454545454545</v>
       </c>
-      <c r="R10" s="48">
+      <c r="R10" s="47">
         <f>SUM(R5:R8)</f>
         <v>0.3545454545454545</v>
       </c>
-      <c r="S10" s="7"/>
-      <c r="T10" s="22">
+      <c r="S10" s="6"/>
+      <c r="T10" s="21">
         <f>SUM(O5:R8)</f>
         <v>1</v>
       </c>
-      <c r="U10" s="11"/>
-      <c r="V10" s="1"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="10"/>
-      <c r="Z10" s="19">
+      <c r="U10" s="10"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="18">
         <f>SUM(Z5:Z8)</f>
         <v>21</v>
       </c>
-      <c r="AA10" s="19">
+      <c r="AA10" s="18">
         <f>SUM(AA5:AA8)</f>
         <v>18</v>
       </c>
-      <c r="AB10" s="19">
+      <c r="AB10" s="18">
         <f>SUM(AB5:AB8)</f>
         <v>27</v>
       </c>
-      <c r="AC10" s="19">
+      <c r="AC10" s="18">
         <f>SUM(AC5:AC8)</f>
         <v>32</v>
       </c>
-      <c r="AD10" s="7"/>
-      <c r="AE10" s="11"/>
-    </row>
-    <row r="11" spans="1:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="9"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="1"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="1"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="10"/>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
-      <c r="AB11" s="7"/>
-      <c r="AC11" s="7"/>
-      <c r="AD11" s="7"/>
-      <c r="AE11" s="11"/>
-    </row>
-    <row r="12" spans="1:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="6"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="12" t="s">
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="10"/>
+    </row>
+    <row r="11" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="10"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="10"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="10"/>
+    </row>
+    <row r="12" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="5"/>
+      <c r="D12" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="22">
         <f>(D5+E6+F7+G8)/I10</f>
         <v>0.74545454545454548</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="1"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="14"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="1"/>
-      <c r="X12" s="13"/>
-      <c r="Y12" s="14"/>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="14"/>
-      <c r="AB12" s="14"/>
-      <c r="AC12" s="14"/>
-      <c r="AD12" s="14"/>
-      <c r="AE12" s="15"/>
-    </row>
-    <row r="13" spans="1:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="13"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="X13" s="1"/>
-      <c r="AE13" s="1"/>
-    </row>
-    <row r="14" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="AB14" s="1"/>
-      <c r="AE14" s="1"/>
-    </row>
-    <row r="15" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="47" t="s">
+      <c r="J12" s="10"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="13"/>
+      <c r="U12" s="14"/>
+      <c r="X12" s="12"/>
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="13"/>
+      <c r="AB12" s="13"/>
+      <c r="AC12" s="13"/>
+      <c r="AD12" s="13"/>
+      <c r="AE12" s="14"/>
+    </row>
+    <row r="13" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="12"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="35" t="s">
+      <c r="G15" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="T15" s="69" t="s">
+      <c r="T15" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="X15" s="1"/>
-      <c r="AB15" s="1"/>
-    </row>
-    <row r="16" spans="1:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="37" t="str">
+    </row>
+    <row r="16" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="36" t="str">
         <f>D4</f>
         <v>A</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="39">
         <f>ABS(T5-O10)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="39">
         <f>2*MIN(T5-O5,O10-O5)</f>
         <v>0.14545454545454548</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="48">
         <f>2*(Z10-D5)/I10</f>
         <v>0.14545454545454545</v>
       </c>
-      <c r="G16" s="40">
+      <c r="G16" s="39">
         <f>E16-F16</f>
         <v>0</v>
       </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="T16" s="69" t="s">
+      <c r="T16" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="X16" s="1"/>
-      <c r="AB16" s="1"/>
-    </row>
-    <row r="17" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="38" t="str">
+    </row>
+    <row r="17" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="37" t="str">
         <f>E4</f>
         <v>B</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="40">
         <f>ABS(T6-P10)</f>
         <v>1.8181818181818188E-2</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="40">
         <f>2*MIN(T6-P6,P10-P6)</f>
         <v>0.2</v>
       </c>
-      <c r="F17" s="50">
+      <c r="F17" s="49">
         <f>2*(AA10-E6)/I10</f>
         <v>0.14545454545454545</v>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="40">
         <f>E17-F17</f>
         <v>5.4545454545454564E-2</v>
       </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="X17" s="1"/>
-      <c r="AB17" s="1"/>
-    </row>
-    <row r="18" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="38" t="str">
+    </row>
+    <row r="18" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="37" t="str">
         <f>F4</f>
         <v>C</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="40">
         <f>ABS(T7-Q10)</f>
         <v>8.1818181818181818E-2</v>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="40">
         <f>2*MIN(T7-Q7,Q10-Q7)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="50">
+      <c r="F18" s="49">
         <f>2*(AB10-F7)/I10</f>
         <v>0</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="40">
         <f>E18-F18</f>
         <v>0</v>
       </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="2"/>
-      <c r="Q18" s="1"/>
-      <c r="AB18" s="1"/>
-    </row>
-    <row r="19" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="39" t="str">
+    </row>
+    <row r="19" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="38" t="str">
         <f>G4</f>
         <v>D</v>
       </c>
-      <c r="D19" s="42">
+      <c r="D19" s="41">
         <f>ABS(T8-R10)</f>
         <v>6.3636363636363602E-2</v>
       </c>
-      <c r="E19" s="42">
+      <c r="E19" s="41">
         <f>2*MIN(T8-R8,R10-R8)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="51">
+      <c r="F19" s="50">
         <f>2*(AC10-G8)/I10</f>
         <v>0</v>
       </c>
-      <c r="G19" s="42">
+      <c r="G19" s="41">
         <f>E19-F19</f>
         <v>0</v>
       </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="68" t="s">
+    </row>
+    <row r="21" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C21" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="65">
+      <c r="D21" s="64">
         <f>SUM(D16:D19)/2</f>
         <v>8.1818181818181804E-2</v>
       </c>
-      <c r="E21" s="65">
+      <c r="E21" s="64">
         <f>SUM(E16:E19)/2</f>
         <v>0.17272727272727273</v>
       </c>
-      <c r="F21" s="65">
+      <c r="F21" s="64">
         <f>SUM(F16:F19)/2</f>
         <v>0.14545454545454545</v>
       </c>
-      <c r="G21" s="65">
+      <c r="G21" s="64">
         <f>SUM(G16:G19)/2</f>
         <v>2.7272727272727282E-2</v>
       </c>

--- a/xls/Pontius.xlsx
+++ b/xls/Pontius.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2025/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_00243C141A561EB39BEA2655A4FC3EF71297758D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DC26D3F-4019-4DA1-9AE7-E39AF7C18F4A}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="11_00243C141A561EB39BEA2655A4FC3EF71297758D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72ACC8D1-87C6-4144-93C4-F165A8BF76DD}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="2085" windowWidth="26610" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="matriz_conf" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="24">
   <si>
     <t>A</t>
   </si>
@@ -108,12 +108,6 @@
   </si>
   <si>
     <t>Proporção Real</t>
-  </si>
-  <si>
-    <t>#http://www.dpi.inpe.br/~camilo/estatistica</t>
-  </si>
-  <si>
-    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2024</t>
   </si>
   <si>
     <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2025</t>
@@ -184,9 +178,8 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -209,7 +202,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -594,21 +587,6 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -635,7 +613,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -715,9 +693,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -736,10 +711,6 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -795,13 +766,13 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -812,7 +783,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -824,6 +795,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -913,13 +899,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.8181818181818188E-2</c:v>
+                  <c:v>1.5000000000000013E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.1818181818181818E-2</c:v>
+                  <c:v>7.4999999999999956E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.3636363636363602E-2</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -977,13 +963,13 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.14545454545454545</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14545454545454545</c:v>
+                  <c:v>7.0000000000000007E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.01</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -1047,7 +1033,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.4545454545454564E-2</c:v>
+                  <c:v>3.999999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1116,6 +1102,7 @@
         <c:crossAx val="601675776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+        <c:majorUnit val="5.000000000000001E-2"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1190,6 +1177,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1480,19 +1471,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:P25"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="2.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="1" customWidth="1"/>
-    <col min="4" max="7" width="8.140625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="2.26953125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" style="1" customWidth="1"/>
+    <col min="4" max="7" width="8.1796875" style="1" customWidth="1"/>
     <col min="8" max="8" width="3" style="1" customWidth="1"/>
-    <col min="9" max="10" width="8.140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="2.42578125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="10" width="8.1796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="2.453125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1503,21 +1494,21 @@
       <c r="I2" s="3"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="5"/>
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="7"/>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="70" t="s">
+    <row r="4" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="65" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="6" t="s">
@@ -1534,23 +1525,23 @@
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="10"/>
-      <c r="N4" s="73" t="s">
+      <c r="N4" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="O4" s="74"/>
-      <c r="P4" s="75"/>
-    </row>
-    <row r="5" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="70"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="70"/>
+    </row>
+    <row r="5" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="65"/>
       <c r="C5" s="6" t="str">
         <f>D4</f>
         <v>A</v>
       </c>
       <c r="D5" s="16">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E5" s="17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" s="17">
         <v>0</v>
@@ -1561,63 +1552,63 @@
       <c r="H5" s="6"/>
       <c r="I5" s="18">
         <f>SUM(D5:G5)</f>
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J5" s="10"/>
-      <c r="M5" s="58" t="str">
+      <c r="M5" s="53" t="str">
         <f>C5</f>
         <v>A</v>
       </c>
-      <c r="N5" s="61">
+      <c r="N5" s="56">
         <v>0.25</v>
       </c>
-      <c r="O5" s="53">
+      <c r="O5" s="48">
         <v>0.01</v>
       </c>
-      <c r="P5" s="54">
+      <c r="P5" s="49">
         <v>0.01</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="70"/>
+    <row r="6" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="65"/>
       <c r="C6" s="6" t="str">
         <f>E4</f>
         <v>B</v>
       </c>
       <c r="D6" s="19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="20">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F6" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="18">
         <f>SUM(D6:G6)</f>
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J6" s="10"/>
-      <c r="M6" s="59" t="str">
+      <c r="M6" s="54" t="str">
         <f>C6</f>
         <v>B</v>
       </c>
-      <c r="N6" s="62">
+      <c r="N6" s="57">
         <v>0.25</v>
       </c>
-      <c r="O6" s="52">
+      <c r="O6" s="47">
         <v>0.02</v>
       </c>
-      <c r="P6" s="55">
+      <c r="P6" s="50">
         <v>0.95</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="70"/>
+    <row r="7" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="65"/>
       <c r="C7" s="6" t="str">
         <f>F4</f>
         <v>C</v>
@@ -1626,36 +1617,36 @@
         <v>0</v>
       </c>
       <c r="E7" s="20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7" s="20">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="G7" s="24">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="18">
         <f>SUM(D7:G7)</f>
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="J7" s="10"/>
-      <c r="M7" s="59" t="str">
+      <c r="M7" s="54" t="str">
         <f>C7</f>
         <v>C</v>
       </c>
-      <c r="N7" s="62">
+      <c r="N7" s="57">
         <v>0.25</v>
       </c>
-      <c r="O7" s="52">
+      <c r="O7" s="47">
         <v>0.95</v>
       </c>
-      <c r="P7" s="55">
+      <c r="P7" s="50">
         <v>0.03</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="70"/>
+    <row r="8" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="65"/>
       <c r="C8" s="6" t="str">
         <f>G4</f>
         <v>D</v>
@@ -1670,33 +1661,33 @@
         <v>0</v>
       </c>
       <c r="G8" s="27">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="18">
         <f>SUM(D8:G8)</f>
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J8" s="10"/>
-      <c r="M8" s="60" t="str">
+      <c r="M8" s="55" t="str">
         <f>C8</f>
         <v>D</v>
       </c>
-      <c r="N8" s="63">
+      <c r="N8" s="58">
         <f>1-SUM(N5:N7)</f>
         <v>0.25</v>
       </c>
-      <c r="O8" s="56">
+      <c r="O8" s="51">
         <f>1-SUM(O5:O7)</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="P8" s="57">
+      <c r="P8" s="52">
         <f>1-SUM(P5:P7)</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="70"/>
+    <row r="9" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="65"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
@@ -1708,48 +1699,48 @@
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
       <c r="D10" s="18">
         <f>SUM(D5:D8)</f>
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E10" s="18">
         <f>SUM(E5:E8)</f>
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="F10" s="18">
         <f>SUM(F5:F8)</f>
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="G10" s="18">
         <f>SUM(G5:G8)</f>
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="21">
         <f>SUM(D5:G8)</f>
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="J10" s="10"/>
       <c r="M10" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="N10" s="65">
-        <f>$D17*N5+$D18*N6+$D19*N7+$D20*N8</f>
-        <v>0.7185857620640228</v>
-      </c>
-      <c r="O10" s="65">
-        <f>$D17*O5+$D18*O6+$D19*O7+$D20*O8</f>
-        <v>0.98129638477464554</v>
-      </c>
-      <c r="P10" s="66">
-        <f>$D17*P5+$D18*P6+$D19*P7+$D20*P8</f>
-        <v>0.45743908265647393</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N10" s="71">
+        <f>$F17*N5+$F18*N6+$F19*N7+$F20*N8</f>
+        <v>0.83679183135704871</v>
+      </c>
+      <c r="O10" s="71">
+        <f t="shared" ref="O10:P10" si="0">$F17*O5+$F18*O6+$F19*O7+$F20*O8</f>
+        <v>0.77310935441370221</v>
+      </c>
+      <c r="P10" s="71">
+        <f t="shared" si="0"/>
+        <v>0.76405138339920953</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="8"/>
       <c r="C11" s="9"/>
       <c r="D11" s="6"/>
@@ -1760,18 +1751,18 @@
       <c r="I11" s="6"/>
       <c r="J11" s="10"/>
     </row>
-    <row r="12" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="5"/>
-      <c r="D12" s="51" t="s">
+      <c r="D12" s="46" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="22">
         <f>(D5+E6+F7+G8)/I10</f>
-        <v>0.74545454545454548</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="J12" s="10"/>
     </row>
-    <row r="13" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="12"/>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
@@ -1782,142 +1773,142 @@
       <c r="I13" s="13"/>
       <c r="J13" s="14"/>
     </row>
-    <row r="14" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="71" t="s">
+    <row r="14" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="E15" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="34" t="s">
+      <c r="F15" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="34" t="s">
+      <c r="G15" s="61" t="s">
         <v>13</v>
       </c>
       <c r="H15" s="15"/>
     </row>
-    <row r="16" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C16" s="72"/>
-      <c r="D16" s="35" t="s">
+    <row r="16" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="67"/>
+      <c r="D16" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="35" t="s">
+      <c r="F16" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="42" t="s">
+      <c r="G16" s="62" t="s">
         <v>9</v>
       </c>
       <c r="H16" s="15"/>
     </row>
-    <row r="17" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="36" t="str">
+    <row r="17" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="35" t="str">
         <f>D4</f>
         <v>A</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="72">
         <f>D5/D10</f>
-        <v>0.61904761904761907</v>
-      </c>
-      <c r="E17" s="39">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="E17" s="72">
         <f>1-D17</f>
-        <v>0.38095238095238093</v>
-      </c>
-      <c r="F17" s="39">
+        <v>0.18181818181818177</v>
+      </c>
+      <c r="F17" s="72">
         <f>D5/I5</f>
-        <v>0.61904761904761907</v>
-      </c>
-      <c r="G17" s="43">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="G17" s="73">
         <f>1-F17</f>
-        <v>0.38095238095238093</v>
-      </c>
-    </row>
-    <row r="18" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="37" t="str">
+        <v>0.18181818181818177</v>
+      </c>
+    </row>
+    <row r="18" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="36" t="str">
         <f>E4</f>
         <v>B</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="74">
         <f>E6/E10</f>
-        <v>0.43478260869565216</v>
-      </c>
-      <c r="E18" s="40">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="E18" s="74">
         <f>1-D18</f>
-        <v>0.56521739130434789</v>
-      </c>
-      <c r="F18" s="40">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="F18" s="74">
         <f>E6/I6</f>
-        <v>0.47619047619047616</v>
-      </c>
-      <c r="G18" s="44">
+        <v>0.76086956521739135</v>
+      </c>
+      <c r="G18" s="75">
         <f>1-F18</f>
-        <v>0.52380952380952384</v>
-      </c>
-    </row>
-    <row r="19" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="37" t="str">
+        <v>0.23913043478260865</v>
+      </c>
+    </row>
+    <row r="19" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="36" t="str">
         <f>F4</f>
         <v>C</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="74">
         <f>F7/F10</f>
-        <v>1</v>
-      </c>
-      <c r="E19" s="40">
+        <v>0.98148148148148151</v>
+      </c>
+      <c r="E19" s="74">
         <f>1-D19</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="40">
+        <v>1.851851851851849E-2</v>
+      </c>
+      <c r="F19" s="74">
         <f>F7/I7</f>
-        <v>0.75</v>
-      </c>
-      <c r="G19" s="44">
+        <v>0.76811594202898548</v>
+      </c>
+      <c r="G19" s="75">
         <f>1-F19</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="20" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C20" s="38" t="str">
+        <v>0.23188405797101452</v>
+      </c>
+    </row>
+    <row r="20" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="37" t="str">
         <f>G4</f>
         <v>D</v>
       </c>
-      <c r="D20" s="41">
+      <c r="D20" s="76">
         <f>G8/G10</f>
-        <v>0.82051282051282048</v>
-      </c>
-      <c r="E20" s="41">
+        <v>0.8125</v>
+      </c>
+      <c r="E20" s="76">
         <f>1-D20</f>
-        <v>0.17948717948717952</v>
-      </c>
-      <c r="F20" s="41">
+        <v>0.1875</v>
+      </c>
+      <c r="F20" s="76">
         <f>G8/I8</f>
         <v>1</v>
       </c>
-      <c r="G20" s="45">
+      <c r="G20" s="77">
         <f>1-F20</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C25" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1935,32 +1926,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AE21"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="2.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="1" customWidth="1"/>
-    <col min="4" max="7" width="8.140625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="2.26953125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" style="1" customWidth="1"/>
+    <col min="4" max="7" width="8.1796875" style="1" customWidth="1"/>
     <col min="8" max="8" width="3" style="1" customWidth="1"/>
-    <col min="9" max="10" width="8.140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="2.42578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="1"/>
-    <col min="13" max="13" width="2.28515625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="7.42578125" style="1" customWidth="1"/>
-    <col min="15" max="18" width="8.140625" style="1" customWidth="1"/>
+    <col min="9" max="10" width="8.1796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="2.453125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.1796875" style="1"/>
+    <col min="13" max="13" width="2.26953125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.453125" style="1" customWidth="1"/>
+    <col min="15" max="18" width="8.1796875" style="1" customWidth="1"/>
     <col min="19" max="19" width="3" style="1" customWidth="1"/>
-    <col min="20" max="21" width="8.140625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="2.42578125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" style="1"/>
-    <col min="24" max="24" width="2.28515625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="7.42578125" style="1" customWidth="1"/>
-    <col min="26" max="29" width="8.140625" style="1" customWidth="1"/>
+    <col min="20" max="21" width="8.1796875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="2.453125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.1796875" style="1"/>
+    <col min="24" max="24" width="2.26953125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="7.453125" style="1" customWidth="1"/>
+    <col min="26" max="29" width="8.1796875" style="1" customWidth="1"/>
     <col min="30" max="30" width="3" style="1" customWidth="1"/>
-    <col min="31" max="31" width="2.42578125" style="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="31" max="31" width="2.453125" style="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1992,41 +1983,41 @@
       <c r="AD2" s="3"/>
       <c r="AE2" s="4"/>
     </row>
-    <row r="3" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="5"/>
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="7"/>
       <c r="K3" s="6"/>
       <c r="M3" s="5"/>
-      <c r="O3" s="69" t="s">
+      <c r="O3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="69"/>
-      <c r="Q3" s="69"/>
-      <c r="R3" s="69"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
       <c r="U3" s="7"/>
       <c r="V3" s="6"/>
       <c r="X3" s="5"/>
-      <c r="Z3" s="69" t="s">
+      <c r="Z3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="AA3" s="69"/>
-      <c r="AB3" s="69"/>
-      <c r="AC3" s="69"/>
+      <c r="AA3" s="64"/>
+      <c r="AB3" s="64"/>
+      <c r="AC3" s="64"/>
       <c r="AD3" s="6"/>
       <c r="AE3" s="7"/>
     </row>
-    <row r="4" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="70" t="s">
+    <row r="4" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="65" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="6" t="s">
@@ -2043,7 +2034,7 @@
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="10"/>
-      <c r="M4" s="70" t="s">
+      <c r="M4" s="65" t="s">
         <v>6</v>
       </c>
       <c r="O4" s="6" t="s">
@@ -2060,7 +2051,7 @@
       </c>
       <c r="T4" s="9"/>
       <c r="U4" s="10"/>
-      <c r="X4" s="70" t="s">
+      <c r="X4" s="65" t="s">
         <v>6</v>
       </c>
       <c r="Z4" s="6" t="s">
@@ -2077,19 +2068,19 @@
       </c>
       <c r="AE4" s="10"/>
     </row>
-    <row r="5" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="70"/>
+    <row r="5" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="65"/>
       <c r="C5" s="6" t="str">
         <f>D4</f>
         <v>A</v>
       </c>
       <c r="D5" s="16">
         <f>matriz_conf!D5</f>
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E5" s="17">
         <f>matriz_conf!E5</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" s="17">
         <f>matriz_conf!F5</f>
@@ -2102,21 +2093,21 @@
       <c r="H5" s="6"/>
       <c r="I5" s="18">
         <f>SUM(D5:G5)</f>
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J5" s="10"/>
-      <c r="M5" s="70"/>
+      <c r="M5" s="65"/>
       <c r="N5" s="6" t="str">
         <f>O4</f>
         <v>A</v>
       </c>
       <c r="O5" s="28">
         <f t="shared" ref="O5:R8" si="0">D5/$I$10</f>
-        <v>0.11818181818181818</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="P5" s="29">
         <f t="shared" si="0"/>
-        <v>7.2727272727272724E-2</v>
+        <v>0.03</v>
       </c>
       <c r="Q5" s="17">
         <f t="shared" si="0"/>
@@ -2127,23 +2118,23 @@
         <v>0</v>
       </c>
       <c r="S5" s="6"/>
-      <c r="T5" s="47">
+      <c r="T5" s="42">
         <f>SUM(O5:R5)</f>
-        <v>0.19090909090909092</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="U5" s="10"/>
-      <c r="X5" s="70"/>
+      <c r="X5" s="65"/>
       <c r="Y5" s="6" t="str">
         <f>Z4</f>
         <v>A</v>
       </c>
       <c r="Z5" s="16">
         <f>MIN(D5,D5)</f>
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AA5" s="17">
         <f>MIN(E5,D6)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB5" s="17">
         <f>MIN(F5,D7)</f>
@@ -2156,77 +2147,77 @@
       <c r="AD5" s="6"/>
       <c r="AE5" s="10"/>
     </row>
-    <row r="6" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="70"/>
+    <row r="6" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="65"/>
       <c r="C6" s="6" t="str">
         <f>E4</f>
         <v>B</v>
       </c>
       <c r="D6" s="19">
         <f>matriz_conf!D6</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="20">
         <f>matriz_conf!E6</f>
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F6" s="20">
         <f>matriz_conf!F6</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="24">
         <f>matriz_conf!G6</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="18">
         <f>SUM(D6:G6)</f>
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J6" s="10"/>
-      <c r="M6" s="70"/>
+      <c r="M6" s="65"/>
       <c r="N6" s="6" t="str">
         <f>P4</f>
         <v>B</v>
       </c>
       <c r="O6" s="30">
         <f t="shared" si="0"/>
-        <v>7.2727272727272724E-2</v>
+        <v>0.03</v>
       </c>
       <c r="P6" s="31">
         <f t="shared" si="0"/>
-        <v>9.0909090909090912E-2</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="Q6" s="20">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="R6" s="24">
         <f t="shared" si="0"/>
-        <v>2.7272727272727271E-2</v>
+        <v>0.02</v>
       </c>
       <c r="S6" s="6"/>
-      <c r="T6" s="47">
+      <c r="T6" s="42">
         <f>SUM(O6:R6)</f>
-        <v>0.19090909090909092</v>
+        <v>0.22999999999999998</v>
       </c>
       <c r="U6" s="10"/>
-      <c r="X6" s="70"/>
+      <c r="X6" s="65"/>
       <c r="Y6" s="6" t="str">
         <f>AA4</f>
         <v>B</v>
       </c>
       <c r="Z6" s="19">
         <f>MIN(D6,E5)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA6" s="20">
         <f>MIN(E6,E6)</f>
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AB6" s="20">
         <f>MIN(F6,E7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" s="24">
         <f>MIN(G6,E8)</f>
@@ -2235,8 +2226,8 @@
       <c r="AD6" s="6"/>
       <c r="AE6" s="10"/>
     </row>
-    <row r="7" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="70"/>
+    <row r="7" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="65"/>
       <c r="C7" s="6" t="str">
         <f>F4</f>
         <v>C</v>
@@ -2247,23 +2238,23 @@
       </c>
       <c r="E7" s="20">
         <f>matriz_conf!E7</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7" s="20">
         <f>matriz_conf!F7</f>
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="G7" s="24">
         <f>matriz_conf!G7</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="18">
         <f>SUM(D7:G7)</f>
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="J7" s="10"/>
-      <c r="M7" s="70"/>
+      <c r="M7" s="65"/>
       <c r="N7" s="6" t="str">
         <f>Q4</f>
         <v>C</v>
@@ -2274,23 +2265,23 @@
       </c>
       <c r="P7" s="31">
         <f t="shared" si="0"/>
-        <v>4.5454545454545456E-2</v>
+        <v>0.04</v>
       </c>
       <c r="Q7" s="31">
         <f t="shared" si="0"/>
-        <v>0.24545454545454545</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="R7" s="32">
         <f t="shared" si="0"/>
-        <v>3.6363636363636362E-2</v>
+        <v>0.04</v>
       </c>
       <c r="S7" s="6"/>
-      <c r="T7" s="47">
+      <c r="T7" s="42">
         <f>SUM(O7:R7)</f>
-        <v>0.32727272727272727</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="U7" s="10"/>
-      <c r="X7" s="70"/>
+      <c r="X7" s="65"/>
       <c r="Y7" s="6" t="str">
         <f>AB4</f>
         <v>C</v>
@@ -2301,11 +2292,11 @@
       </c>
       <c r="AA7" s="20">
         <f>MIN(E7,F6)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" s="20">
         <f>MIN(F7,F7)</f>
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="AC7" s="24">
         <f>MIN(G7,F8)</f>
@@ -2314,8 +2305,8 @@
       <c r="AD7" s="6"/>
       <c r="AE7" s="10"/>
     </row>
-    <row r="8" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="70"/>
+    <row r="8" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="65"/>
       <c r="C8" s="6" t="str">
         <f>G4</f>
         <v>D</v>
@@ -2334,15 +2325,15 @@
       </c>
       <c r="G8" s="27">
         <f>matriz_conf!G8</f>
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="18">
         <f>SUM(D8:G8)</f>
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="J8" s="10"/>
-      <c r="M8" s="70"/>
+      <c r="M8" s="65"/>
       <c r="N8" s="6" t="str">
         <f>R4</f>
         <v>D</v>
@@ -2361,15 +2352,15 @@
       </c>
       <c r="R8" s="33">
         <f t="shared" si="0"/>
-        <v>0.29090909090909089</v>
+        <v>0.26</v>
       </c>
       <c r="S8" s="6"/>
-      <c r="T8" s="47">
+      <c r="T8" s="42">
         <f>SUM(O8:R8)</f>
-        <v>0.29090909090909089</v>
+        <v>0.26</v>
       </c>
       <c r="U8" s="10"/>
-      <c r="X8" s="70"/>
+      <c r="X8" s="65"/>
       <c r="Y8" s="6" t="str">
         <f>AC4</f>
         <v>D</v>
@@ -2388,13 +2379,13 @@
       </c>
       <c r="AC8" s="27">
         <f>MIN(G8,G8)</f>
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="AD8" s="6"/>
       <c r="AE8" s="10"/>
     </row>
-    <row r="9" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="70"/>
+    <row r="9" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="65"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
@@ -2402,7 +2393,7 @@
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="10"/>
-      <c r="M9" s="70"/>
+      <c r="M9" s="65"/>
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
@@ -2410,7 +2401,7 @@
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
       <c r="U9" s="10"/>
-      <c r="X9" s="70"/>
+      <c r="X9" s="65"/>
       <c r="Z9" s="6"/>
       <c r="AA9" s="6"/>
       <c r="AB9" s="6"/>
@@ -2418,48 +2409,48 @@
       <c r="AD9" s="6"/>
       <c r="AE9" s="10"/>
     </row>
-    <row r="10" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
       <c r="D10" s="18">
         <f>SUM(D5:D8)</f>
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E10" s="18">
         <f>SUM(E5:E8)</f>
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="F10" s="18">
         <f>SUM(F5:F8)</f>
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="G10" s="18">
         <f>SUM(G5:G8)</f>
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="21">
         <f>SUM(D5:G8)</f>
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="J10" s="10"/>
       <c r="M10" s="8"/>
       <c r="N10" s="9"/>
-      <c r="O10" s="47">
+      <c r="O10" s="42">
         <f>SUM(O5:O8)</f>
-        <v>0.19090909090909092</v>
-      </c>
-      <c r="P10" s="47">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="P10" s="42">
         <f>SUM(P5:P8)</f>
-        <v>0.20909090909090911</v>
-      </c>
-      <c r="Q10" s="47">
+        <v>0.245</v>
+      </c>
+      <c r="Q10" s="42">
         <f>SUM(Q5:Q8)</f>
-        <v>0.24545454545454545</v>
-      </c>
-      <c r="R10" s="47">
+        <v>0.27</v>
+      </c>
+      <c r="R10" s="42">
         <f>SUM(R5:R8)</f>
-        <v>0.3545454545454545</v>
+        <v>0.32</v>
       </c>
       <c r="S10" s="6"/>
       <c r="T10" s="21">
@@ -2471,24 +2462,24 @@
       <c r="Y10" s="9"/>
       <c r="Z10" s="18">
         <f>SUM(Z5:Z8)</f>
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="AA10" s="18">
         <f>SUM(AA5:AA8)</f>
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="AB10" s="18">
         <f>SUM(AB5:AB8)</f>
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="AC10" s="18">
         <f>SUM(AC5:AC8)</f>
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="AD10" s="6"/>
       <c r="AE10" s="10"/>
     </row>
-    <row r="11" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="8"/>
       <c r="C11" s="9"/>
       <c r="D11" s="6"/>
@@ -2516,14 +2507,14 @@
       <c r="AD11" s="6"/>
       <c r="AE11" s="10"/>
     </row>
-    <row r="12" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="5"/>
       <c r="D12" s="11" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="22">
         <f>(D5+E6+F7+G8)/I10</f>
-        <v>0.74545454545454548</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="J12" s="10"/>
       <c r="M12" s="12"/>
@@ -2544,7 +2535,7 @@
       <c r="AD12" s="13"/>
       <c r="AE12" s="14"/>
     </row>
-    <row r="13" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="12"/>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
@@ -2555,9 +2546,9 @@
       <c r="I13" s="13"/>
       <c r="J13" s="14"/>
     </row>
-    <row r="14" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="46" t="s">
+    <row r="14" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="41" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="34" t="s">
@@ -2572,120 +2563,123 @@
       <c r="G15" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="T15" s="68" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="36" t="str">
+      <c r="T15" s="63" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="35" t="str">
         <f>D4</f>
         <v>A</v>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="38">
         <f>ABS(T5-O10)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="38">
         <f>2*MIN(T5-O5,O10-O5)</f>
-        <v>0.14545454545454548</v>
-      </c>
-      <c r="F16" s="48">
+        <v>0.06</v>
+      </c>
+      <c r="F16" s="43">
         <f>2*(Z10-D5)/I10</f>
-        <v>0.14545454545454545</v>
-      </c>
-      <c r="G16" s="39">
+        <v>0.06</v>
+      </c>
+      <c r="G16" s="38">
         <f>E16-F16</f>
         <v>0</v>
       </c>
-      <c r="T16" s="68" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="37" t="str">
+      <c r="T16" s="63" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="3:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="36" t="str">
         <f>E4</f>
         <v>B</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="39">
         <f>ABS(T6-P10)</f>
-        <v>1.8181818181818188E-2</v>
-      </c>
-      <c r="E17" s="40">
+        <v>1.5000000000000013E-2</v>
+      </c>
+      <c r="E17" s="39">
         <f>2*MIN(T6-P6,P10-P6)</f>
-        <v>0.2</v>
-      </c>
-      <c r="F17" s="49">
+        <v>0.10999999999999999</v>
+      </c>
+      <c r="F17" s="44">
         <f>2*(AA10-E6)/I10</f>
-        <v>0.14545454545454545</v>
-      </c>
-      <c r="G17" s="40">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G17" s="39">
         <f>E17-F17</f>
-        <v>5.4545454545454564E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="37" t="str">
+        <v>3.999999999999998E-2</v>
+      </c>
+      <c r="T17" s="63" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="36" t="str">
         <f>F4</f>
         <v>C</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="39">
         <f>ABS(T7-Q10)</f>
-        <v>8.1818181818181818E-2</v>
-      </c>
-      <c r="E18" s="40">
+        <v>7.4999999999999956E-2</v>
+      </c>
+      <c r="E18" s="39">
         <f>2*MIN(T7-Q7,Q10-Q7)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="49">
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="F18" s="44">
         <f>2*(AB10-F7)/I10</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="40">
+        <v>0.01</v>
+      </c>
+      <c r="G18" s="39">
         <f>E18-F18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="38" t="str">
+    <row r="19" spans="3:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="37" t="str">
         <f>G4</f>
         <v>D</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="40">
         <f>ABS(T8-R10)</f>
-        <v>6.3636363636363602E-2</v>
-      </c>
-      <c r="E19" s="41">
+        <v>0.06</v>
+      </c>
+      <c r="E19" s="40">
         <f>2*MIN(T8-R8,R10-R8)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="50">
+      <c r="F19" s="45">
         <f>2*(AC10-G8)/I10</f>
         <v>0</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="40">
         <f>E19-F19</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.2">
-      <c r="C21" s="67" t="s">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C21" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="64">
+      <c r="D21" s="59">
         <f>SUM(D16:D19)/2</f>
-        <v>8.1818181818181804E-2</v>
-      </c>
-      <c r="E21" s="64">
+        <v>7.4999999999999983E-2</v>
+      </c>
+      <c r="E21" s="59">
         <f>SUM(E16:E19)/2</f>
-        <v>0.17272727272727273</v>
-      </c>
-      <c r="F21" s="64">
+        <v>0.09</v>
+      </c>
+      <c r="F21" s="59">
         <f>SUM(F16:F19)/2</f>
-        <v>0.14545454545454545</v>
-      </c>
-      <c r="G21" s="64">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G21" s="59">
         <f>SUM(G16:G19)/2</f>
-        <v>2.7272727272727282E-2</v>
+        <v>1.999999999999999E-2</v>
       </c>
     </row>
   </sheetData>

--- a/xls/Pontius.xlsx
+++ b/xls/Pontius.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2025/xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2026/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="11_00243C141A561EB39BEA2655A4FC3EF71297758D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72ACC8D1-87C6-4144-93C4-F165A8BF76DD}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="11_00243C141A561EB39BEA2655A4FC3EF71297758D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E5CA06A-5014-4E84-8904-25B7A0C434B2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="matriz_conf" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="23">
   <si>
     <t>A</t>
   </si>
@@ -110,13 +110,10 @@
     <t>Proporção Real</t>
   </si>
   <si>
-    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2025</t>
+    <t>#https://cdrenno.github.io/Estatistica/</t>
   </si>
   <si>
-    <t>#http://urlib.net/8JMKD2USNRW34T/4D6DMD2</t>
-  </si>
-  <si>
-    <t>#https://cdrenno.github.io/Estatistica/</t>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2026</t>
   </si>
 </sst>
 </file>
@@ -127,7 +124,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -175,12 +172,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -613,7 +604,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -773,7 +764,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -795,21 +800,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1179,10 +1169,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -1471,19 +1457,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:P25"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="2.26953125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.453125" style="1" customWidth="1"/>
-    <col min="4" max="7" width="8.1796875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="2.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="1" customWidth="1"/>
+    <col min="4" max="7" width="8.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="3" style="1" customWidth="1"/>
-    <col min="9" max="10" width="8.1796875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="2.453125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.1796875" style="1"/>
+    <col min="9" max="10" width="8.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="2.42578125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1494,21 +1480,21 @@
       <c r="I2" s="3"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5"/>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="7"/>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="65" t="s">
+    <row r="4" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="71" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="6" t="s">
@@ -1525,14 +1511,14 @@
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="10"/>
-      <c r="N4" s="68" t="s">
+      <c r="N4" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="O4" s="69"/>
-      <c r="P4" s="70"/>
-    </row>
-    <row r="5" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="65"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="76"/>
+    </row>
+    <row r="5" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="71"/>
       <c r="C5" s="6" t="str">
         <f>D4</f>
         <v>A</v>
@@ -1569,8 +1555,8 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="65"/>
+    <row r="6" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="71"/>
       <c r="C6" s="6" t="str">
         <f>E4</f>
         <v>B</v>
@@ -1607,8 +1593,8 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="65"/>
+    <row r="7" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="71"/>
       <c r="C7" s="6" t="str">
         <f>F4</f>
         <v>C</v>
@@ -1645,8 +1631,8 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="65"/>
+    <row r="8" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="71"/>
       <c r="C8" s="6" t="str">
         <f>G4</f>
         <v>D</v>
@@ -1686,8 +1672,8 @@
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="65"/>
+    <row r="9" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="71"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
@@ -1699,7 +1685,7 @@
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
     </row>
-    <row r="10" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
       <c r="D10" s="18">
@@ -1727,20 +1713,20 @@
       <c r="M10" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="N10" s="71">
+      <c r="N10" s="63">
         <f>$F17*N5+$F18*N6+$F19*N7+$F20*N8</f>
         <v>0.83679183135704871</v>
       </c>
-      <c r="O10" s="71">
+      <c r="O10" s="63">
         <f t="shared" ref="O10:P10" si="0">$F17*O5+$F18*O6+$F19*O7+$F20*O8</f>
         <v>0.77310935441370221</v>
       </c>
-      <c r="P10" s="71">
+      <c r="P10" s="63">
         <f t="shared" si="0"/>
         <v>0.76405138339920953</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="8"/>
       <c r="C11" s="9"/>
       <c r="D11" s="6"/>
@@ -1751,7 +1737,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="10"/>
     </row>
-    <row r="12" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5"/>
       <c r="D12" s="46" t="s">
         <v>7</v>
@@ -1762,7 +1748,7 @@
       </c>
       <c r="J12" s="10"/>
     </row>
-    <row r="13" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="12"/>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
@@ -1773,9 +1759,9 @@
       <c r="I13" s="13"/>
       <c r="J13" s="14"/>
     </row>
-    <row r="14" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="66" t="s">
+    <row r="14" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="72" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="61" t="s">
@@ -1792,8 +1778,8 @@
       </c>
       <c r="H15" s="15"/>
     </row>
-    <row r="16" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="67"/>
+    <row r="16" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C16" s="73"/>
       <c r="D16" s="62" t="s">
         <v>11</v>
       </c>
@@ -1808,108 +1794,106 @@
       </c>
       <c r="H16" s="15"/>
     </row>
-    <row r="17" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="35" t="str">
         <f>D4</f>
         <v>A</v>
       </c>
-      <c r="D17" s="72">
+      <c r="D17" s="64">
         <f>D5/D10</f>
         <v>0.81818181818181823</v>
       </c>
-      <c r="E17" s="72">
+      <c r="E17" s="64">
         <f>1-D17</f>
         <v>0.18181818181818177</v>
       </c>
-      <c r="F17" s="72">
+      <c r="F17" s="64">
         <f>D5/I5</f>
         <v>0.81818181818181823</v>
       </c>
-      <c r="G17" s="73">
+      <c r="G17" s="65">
         <f>1-F17</f>
         <v>0.18181818181818177</v>
       </c>
     </row>
-    <row r="18" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="36" t="str">
         <f>E4</f>
         <v>B</v>
       </c>
-      <c r="D18" s="74">
+      <c r="D18" s="66">
         <f>E6/E10</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="E18" s="74">
+      <c r="E18" s="66">
         <f>1-D18</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="F18" s="74">
+      <c r="F18" s="66">
         <f>E6/I6</f>
         <v>0.76086956521739135</v>
       </c>
-      <c r="G18" s="75">
+      <c r="G18" s="67">
         <f>1-F18</f>
         <v>0.23913043478260865</v>
       </c>
     </row>
-    <row r="19" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C19" s="36" t="str">
         <f>F4</f>
         <v>C</v>
       </c>
-      <c r="D19" s="74">
+      <c r="D19" s="66">
         <f>F7/F10</f>
         <v>0.98148148148148151</v>
       </c>
-      <c r="E19" s="74">
+      <c r="E19" s="66">
         <f>1-D19</f>
         <v>1.851851851851849E-2</v>
       </c>
-      <c r="F19" s="74">
+      <c r="F19" s="66">
         <f>F7/I7</f>
         <v>0.76811594202898548</v>
       </c>
-      <c r="G19" s="75">
+      <c r="G19" s="67">
         <f>1-F19</f>
         <v>0.23188405797101452</v>
       </c>
     </row>
-    <row r="20" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="37" t="str">
         <f>G4</f>
         <v>D</v>
       </c>
-      <c r="D20" s="76">
+      <c r="D20" s="68">
         <f>G8/G10</f>
         <v>0.8125</v>
       </c>
-      <c r="E20" s="76">
+      <c r="E20" s="68">
         <f>1-D20</f>
         <v>0.1875</v>
       </c>
-      <c r="F20" s="76">
+      <c r="F20" s="68">
         <f>G8/I8</f>
         <v>1</v>
       </c>
-      <c r="G20" s="77">
+      <c r="G20" s="69">
         <f>1-F20</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
-        <v>23</v>
-      </c>
+    <row r="25" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1926,32 +1910,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AE21"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="2.26953125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.453125" style="1" customWidth="1"/>
-    <col min="4" max="7" width="8.1796875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="2.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="1" customWidth="1"/>
+    <col min="4" max="7" width="8.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="3" style="1" customWidth="1"/>
-    <col min="9" max="10" width="8.1796875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="2.453125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.1796875" style="1"/>
-    <col min="13" max="13" width="2.26953125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="7.453125" style="1" customWidth="1"/>
-    <col min="15" max="18" width="8.1796875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="8.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="2.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="1"/>
+    <col min="13" max="13" width="2.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.42578125" style="1" customWidth="1"/>
+    <col min="15" max="18" width="8.140625" style="1" customWidth="1"/>
     <col min="19" max="19" width="3" style="1" customWidth="1"/>
-    <col min="20" max="21" width="8.1796875" style="1" customWidth="1"/>
-    <col min="22" max="22" width="2.453125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.1796875" style="1"/>
-    <col min="24" max="24" width="2.26953125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="7.453125" style="1" customWidth="1"/>
-    <col min="26" max="29" width="8.1796875" style="1" customWidth="1"/>
+    <col min="20" max="21" width="8.140625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="2.42578125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.140625" style="1"/>
+    <col min="24" max="24" width="2.28515625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="7.42578125" style="1" customWidth="1"/>
+    <col min="26" max="29" width="8.140625" style="1" customWidth="1"/>
     <col min="30" max="30" width="3" style="1" customWidth="1"/>
-    <col min="31" max="31" width="2.453125" style="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.1796875" style="1"/>
+    <col min="31" max="31" width="2.42578125" style="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1983,41 +1967,41 @@
       <c r="AD2" s="3"/>
       <c r="AE2" s="4"/>
     </row>
-    <row r="3" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="5"/>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="7"/>
       <c r="K3" s="6"/>
       <c r="M3" s="5"/>
-      <c r="O3" s="64" t="s">
+      <c r="O3" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
+      <c r="P3" s="70"/>
+      <c r="Q3" s="70"/>
+      <c r="R3" s="70"/>
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
       <c r="U3" s="7"/>
       <c r="V3" s="6"/>
       <c r="X3" s="5"/>
-      <c r="Z3" s="64" t="s">
+      <c r="Z3" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="AA3" s="64"/>
-      <c r="AB3" s="64"/>
-      <c r="AC3" s="64"/>
+      <c r="AA3" s="70"/>
+      <c r="AB3" s="70"/>
+      <c r="AC3" s="70"/>
       <c r="AD3" s="6"/>
       <c r="AE3" s="7"/>
     </row>
-    <row r="4" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="65" t="s">
+    <row r="4" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="71" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="6" t="s">
@@ -2034,7 +2018,7 @@
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="10"/>
-      <c r="M4" s="65" t="s">
+      <c r="M4" s="71" t="s">
         <v>6</v>
       </c>
       <c r="O4" s="6" t="s">
@@ -2051,7 +2035,7 @@
       </c>
       <c r="T4" s="9"/>
       <c r="U4" s="10"/>
-      <c r="X4" s="65" t="s">
+      <c r="X4" s="71" t="s">
         <v>6</v>
       </c>
       <c r="Z4" s="6" t="s">
@@ -2068,8 +2052,8 @@
       </c>
       <c r="AE4" s="10"/>
     </row>
-    <row r="5" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="65"/>
+    <row r="5" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="71"/>
       <c r="C5" s="6" t="str">
         <f>D4</f>
         <v>A</v>
@@ -2096,7 +2080,7 @@
         <v>33</v>
       </c>
       <c r="J5" s="10"/>
-      <c r="M5" s="65"/>
+      <c r="M5" s="71"/>
       <c r="N5" s="6" t="str">
         <f>O4</f>
         <v>A</v>
@@ -2123,7 +2107,7 @@
         <v>0.16500000000000001</v>
       </c>
       <c r="U5" s="10"/>
-      <c r="X5" s="65"/>
+      <c r="X5" s="71"/>
       <c r="Y5" s="6" t="str">
         <f>Z4</f>
         <v>A</v>
@@ -2147,8 +2131,8 @@
       <c r="AD5" s="6"/>
       <c r="AE5" s="10"/>
     </row>
-    <row r="6" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="65"/>
+    <row r="6" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="71"/>
       <c r="C6" s="6" t="str">
         <f>E4</f>
         <v>B</v>
@@ -2175,7 +2159,7 @@
         <v>46</v>
       </c>
       <c r="J6" s="10"/>
-      <c r="M6" s="65"/>
+      <c r="M6" s="71"/>
       <c r="N6" s="6" t="str">
         <f>P4</f>
         <v>B</v>
@@ -2202,7 +2186,7 @@
         <v>0.22999999999999998</v>
       </c>
       <c r="U6" s="10"/>
-      <c r="X6" s="65"/>
+      <c r="X6" s="71"/>
       <c r="Y6" s="6" t="str">
         <f>AA4</f>
         <v>B</v>
@@ -2226,8 +2210,8 @@
       <c r="AD6" s="6"/>
       <c r="AE6" s="10"/>
     </row>
-    <row r="7" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="65"/>
+    <row r="7" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="71"/>
       <c r="C7" s="6" t="str">
         <f>F4</f>
         <v>C</v>
@@ -2254,7 +2238,7 @@
         <v>69</v>
       </c>
       <c r="J7" s="10"/>
-      <c r="M7" s="65"/>
+      <c r="M7" s="71"/>
       <c r="N7" s="6" t="str">
         <f>Q4</f>
         <v>C</v>
@@ -2281,7 +2265,7 @@
         <v>0.34499999999999997</v>
       </c>
       <c r="U7" s="10"/>
-      <c r="X7" s="65"/>
+      <c r="X7" s="71"/>
       <c r="Y7" s="6" t="str">
         <f>AB4</f>
         <v>C</v>
@@ -2305,8 +2289,8 @@
       <c r="AD7" s="6"/>
       <c r="AE7" s="10"/>
     </row>
-    <row r="8" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="65"/>
+    <row r="8" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="71"/>
       <c r="C8" s="6" t="str">
         <f>G4</f>
         <v>D</v>
@@ -2333,7 +2317,7 @@
         <v>52</v>
       </c>
       <c r="J8" s="10"/>
-      <c r="M8" s="65"/>
+      <c r="M8" s="71"/>
       <c r="N8" s="6" t="str">
         <f>R4</f>
         <v>D</v>
@@ -2360,7 +2344,7 @@
         <v>0.26</v>
       </c>
       <c r="U8" s="10"/>
-      <c r="X8" s="65"/>
+      <c r="X8" s="71"/>
       <c r="Y8" s="6" t="str">
         <f>AC4</f>
         <v>D</v>
@@ -2384,8 +2368,8 @@
       <c r="AD8" s="6"/>
       <c r="AE8" s="10"/>
     </row>
-    <row r="9" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="65"/>
+    <row r="9" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="71"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
@@ -2393,7 +2377,7 @@
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="10"/>
-      <c r="M9" s="65"/>
+      <c r="M9" s="71"/>
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
@@ -2401,7 +2385,7 @@
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
       <c r="U9" s="10"/>
-      <c r="X9" s="65"/>
+      <c r="X9" s="71"/>
       <c r="Z9" s="6"/>
       <c r="AA9" s="6"/>
       <c r="AB9" s="6"/>
@@ -2409,7 +2393,7 @@
       <c r="AD9" s="6"/>
       <c r="AE9" s="10"/>
     </row>
-    <row r="10" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
       <c r="D10" s="18">
@@ -2479,7 +2463,7 @@
       <c r="AD10" s="6"/>
       <c r="AE10" s="10"/>
     </row>
-    <row r="11" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="8"/>
       <c r="C11" s="9"/>
       <c r="D11" s="6"/>
@@ -2507,7 +2491,7 @@
       <c r="AD11" s="6"/>
       <c r="AE11" s="10"/>
     </row>
-    <row r="12" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="5"/>
       <c r="D12" s="11" t="s">
         <v>7</v>
@@ -2535,7 +2519,7 @@
       <c r="AD12" s="13"/>
       <c r="AE12" s="14"/>
     </row>
-    <row r="13" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:31" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="12"/>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
@@ -2546,8 +2530,8 @@
       <c r="I13" s="13"/>
       <c r="J13" s="14"/>
     </row>
-    <row r="14" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="41" t="s">
         <v>4</v>
       </c>
@@ -2563,11 +2547,11 @@
       <c r="G15" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="T15" s="63" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="2:31" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="35" t="str">
         <f>D4</f>
         <v>A</v>
@@ -2588,11 +2572,11 @@
         <f>E16-F16</f>
         <v>0</v>
       </c>
-      <c r="T16" s="63" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="3:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="3:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="36" t="str">
         <f>E4</f>
         <v>B</v>
@@ -2613,11 +2597,9 @@
         <f>E17-F17</f>
         <v>3.999999999999998E-2</v>
       </c>
-      <c r="T17" s="63" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T17"/>
+    </row>
+    <row r="18" spans="3:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="36" t="str">
         <f>F4</f>
         <v>C</v>
@@ -2639,7 +2621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C19" s="37" t="str">
         <f>G4</f>
         <v>D</v>
@@ -2661,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="60" t="s">
         <v>19</v>
       </c>
